--- a/data/quality.xlsx
+++ b/data/quality.xlsx
@@ -9,16 +9,20 @@
   <sheets>
     <sheet name="Пояснения" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Качество успеха" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Цена" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Игроки" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Ориентиры" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Цена (онлайн-кооп)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Игроки (онлайн-кооп)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Цена (весь кооп)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Игроки (весь кооп)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Ориентиры" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Пояснения'!$A$1:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Пояснения'!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Качество успеха'!$A$1:$I$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Цена'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Игроки'!$A$1:$H$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ориентиры'!$A$1:$O$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Цена (онлайн-кооп)'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Игроки (онлайн-кооп)'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Цена (весь кооп)'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Игроки (весь кооп)'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Ориентиры'!$A$1:$O$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -533,17 +537,41 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Онлайн-кооп / весь кооп</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Цена и игроки посчитаны отдельно для игр с онлайн-коопом среди главных тегов: двухместные игры в основном локальные, и без этого разреза два эффекта смешиваются.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Осторожно: цена</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Дорогие игры обычно и сделаны с большим вложением. Высокая доля успеха у $15+ — не повод поднять цену, а признак того, что такие игры крупнее. Надёжный вывод — дешевле $5 почти никто не взлетает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Продажи ≈</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Отзывы × 20 … × 60.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B9"/>
+  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1287,7 +1315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1297,6 +1325,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1335,6 +1364,11 @@
           <t>Медиана отзывов</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Примеры</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1343,22 +1377,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>792</v>
+        <v>227</v>
       </c>
       <c r="C2" t="n">
-        <v>10.5</v>
+        <v>16.7</v>
       </c>
       <c r="D2" t="n">
-        <v>8.5</v>
+        <v>12.4</v>
       </c>
       <c r="E2" t="n">
-        <v>12.8</v>
+        <v>22.1</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>13</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>WEBFISHING; Zort; We Were Here Expeditions: The FriendShip; Carry The Glass</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1368,22 +1407,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>629</v>
+        <v>208</v>
       </c>
       <c r="C3" t="n">
-        <v>21.8</v>
+        <v>39.9</v>
       </c>
       <c r="D3" t="n">
-        <v>18.7</v>
+        <v>33.5</v>
       </c>
       <c r="E3" t="n">
-        <v>25.2</v>
+        <v>46.7</v>
       </c>
       <c r="F3" t="n">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
+        <v>48</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Lethal Company; R.E.P.O.; PEAK; Content Warning</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1393,22 +1437,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>260</v>
+        <v>69</v>
       </c>
       <c r="C4" t="n">
-        <v>31.2</v>
+        <v>37.7</v>
       </c>
       <c r="D4" t="n">
-        <v>25.8</v>
+        <v>27.2</v>
       </c>
       <c r="E4" t="n">
-        <v>37</v>
+        <v>49.5</v>
       </c>
       <c r="F4" t="n">
-        <v>8.1</v>
+        <v>10.1</v>
       </c>
       <c r="G4" t="n">
-        <v>37.5</v>
+        <v>63</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FOREWARNED; Mycopunk; Ghost Exile; Gatekeeper</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1418,22 +1467,27 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="D5" t="n">
-        <v>42.3</v>
+        <v>48.4</v>
       </c>
       <c r="E5" t="n">
-        <v>57.7</v>
+        <v>74.8</v>
       </c>
       <c r="F5" t="n">
-        <v>16.2</v>
+        <v>22.9</v>
       </c>
       <c r="G5" t="n">
-        <v>101.5</v>
+        <v>246</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Party Animals; Demonologist; We Were Here Forever; Crime Boss: Rockay City</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1443,26 +1497,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>43</v>
       </c>
       <c r="C6" t="n">
-        <v>58.9</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>50.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>66.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="F6" t="n">
-        <v>34.2</v>
+        <v>53.5</v>
       </c>
       <c r="G6" t="n">
-        <v>197.5</v>
+        <v>1128</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PAYDAY 3; Starship Troopers: Extermination; Roboquest; Ravenswatch</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:H6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1519,7 +1578,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>С онлайн-коопом, %</t>
+          <t>Медиана отзывов</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -1535,26 +1594,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
-        <v>40.6</v>
+        <v>46.3</v>
       </c>
       <c r="D2" t="n">
-        <v>29.5</v>
+        <v>32.1</v>
       </c>
       <c r="E2" t="n">
-        <v>52.9</v>
+        <v>61.3</v>
       </c>
       <c r="F2" t="n">
-        <v>17.2</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Roboquest; We Were Here Forever; BOKURA; Astral Ascent</t>
+          <t>Roboquest; We Were Here Forever; BOKURA; Carry The Glass</t>
         </is>
       </c>
     </row>
@@ -1565,26 +1624,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="C3" t="n">
-        <v>37.5</v>
+        <v>40.8</v>
       </c>
       <c r="D3" t="n">
-        <v>31.2</v>
+        <v>34.6</v>
       </c>
       <c r="E3" t="n">
-        <v>44.2</v>
+        <v>47.4</v>
       </c>
       <c r="F3" t="n">
-        <v>11.5</v>
+        <v>13.9</v>
       </c>
       <c r="G3" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Vampire Survivors; Brotato; The Outlast Trials; PAYDAY 3</t>
+          <t>Content Warning; PAYDAY 3; Inside the Backrooms; Demonologist</t>
         </is>
       </c>
     </row>
@@ -1595,26 +1654,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="C4" t="n">
-        <v>41.7</v>
+        <v>45.9</v>
       </c>
       <c r="D4" t="n">
-        <v>30.1</v>
+        <v>35.7</v>
       </c>
       <c r="E4" t="n">
-        <v>54.3</v>
+        <v>56.4</v>
       </c>
       <c r="F4" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Ready or Not; Killing Floor 3; Labyrinthine; Teenage Mutant Ninja Turtles: Shredder's Revenge</t>
+          <t>R.E.P.O.; Backrooms: Escape Together; Labyrinthine; PANICORE</t>
         </is>
       </c>
     </row>
@@ -1625,26 +1684,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>45.8</v>
+        <v>29.4</v>
       </c>
       <c r="D5" t="n">
-        <v>27.9</v>
+        <v>16.8</v>
       </c>
       <c r="E5" t="n">
-        <v>64.90000000000001</v>
+        <v>46.2</v>
       </c>
       <c r="F5" t="n">
-        <v>12.5</v>
+        <v>5.9</v>
       </c>
       <c r="G5" t="n">
-        <v>54</v>
+        <v>27.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Starship Troopers: Extermination; Zero Hour; Sniper Elite 5; KarmaZoo</t>
+          <t>Starship Troopers: Extermination; BACKROOMS: APPREHENSION; The Backrooms: Survival; Ikki Unite</t>
         </is>
       </c>
     </row>
@@ -1655,26 +1714,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1635</v>
+        <v>212</v>
       </c>
       <c r="C6" t="n">
-        <v>20.1</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>18.2</v>
+        <v>19.7</v>
       </c>
       <c r="E6" t="n">
-        <v>22.1</v>
+        <v>31.2</v>
       </c>
       <c r="F6" t="n">
-        <v>6.7</v>
+        <v>9.9</v>
       </c>
       <c r="G6" t="n">
-        <v>28</v>
+        <v>14.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lethal Company; R.E.P.O.; PEAK; Warhammer 40,000: Space Marine 2</t>
+          <t>Lethal Company; PEAK; WEBFISHING; Party Animals</t>
         </is>
       </c>
     </row>
@@ -1685,6 +1744,440 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Игр</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Набрали 100+, %</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Интервал от</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Интервал до</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Набрали 1000+, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Медиана отзывов</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Примеры</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>до $5</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>792</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vampire Survivors; Brotato; WEBFISHING; Mage Arena</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>$5–9.99</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>629</v>
+      </c>
+      <c r="C3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Lethal Company; R.E.P.O.; PEAK; Content Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>$10–14.99</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>260</v>
+      </c>
+      <c r="C4" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>37</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>The Texas Chain Saw Massacre; Ghost Watchers; Rabbit and Steel; FOREWARNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>$15–19.99</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>160</v>
+      </c>
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Party Animals; Demonologist; We Were Here Forever; Jump Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>$20+</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>146</v>
+      </c>
+      <c r="C6" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ready or Not; Warhammer 40,000: Space Marine 2; Warhammer 40,000: Darktide; The Outlast Trials</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Игроков</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Игр</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Набрали 100+, %</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Интервал от</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Интервал до</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Набрали 1000+, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Медиана отзывов</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Примеры</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>211</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Roboquest; We Were Here Forever; BOKURA; Astral Ascent</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3–4</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>578</v>
+      </c>
+      <c r="C3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vampire Survivors; Warhammer 40,000: Space Marine 2; Brotato; The Outlast Trials</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5–8</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>211</v>
+      </c>
+      <c r="C4" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>R.E.P.O.; Ready or Not; Backrooms: Escape Together; Killing Floor 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>9+</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C5" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Starship Troopers: Extermination; Zero Hour; Sniper Elite 5; Wildgate</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>914</v>
+      </c>
+      <c r="C6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Lethal Company; PEAK; Warhammer 40,000: Darktide; WEBFISHING</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1866,7 +2359,9 @@
       <c r="I3" t="n">
         <v>37</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -2003,7 +2498,9 @@
       <c r="I6" t="n">
         <v>45.1</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
       <c r="K6" t="n">
         <v>2973</v>
       </c>
@@ -2101,7 +2598,9 @@
       <c r="I8" t="n">
         <v>57.1</v>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
       <c r="K8" t="n">
         <v>3536</v>
       </c>
@@ -2148,7 +2647,9 @@
       <c r="I9" t="n">
         <v>27.1</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
@@ -2295,7 +2796,9 @@
       <c r="I12" t="n">
         <v>14.2</v>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>8</v>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -2440,7 +2943,9 @@
       <c r="I15" t="n">
         <v>71.3</v>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>8</v>
+      </c>
       <c r="K15" t="n">
         <v>6553</v>
       </c>
@@ -2495,7 +3000,9 @@
       <c r="I16" t="n">
         <v>31.9</v>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
@@ -2544,7 +3051,9 @@
       <c r="I17" t="n">
         <v>49.1</v>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
@@ -2740,7 +3249,9 @@
       <c r="I21" t="n">
         <v>66.3</v>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>6</v>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
@@ -2928,7 +3439,9 @@
       <c r="I25" t="n">
         <v>66.2</v>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>12</v>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -2973,7 +3486,9 @@
       <c r="I26" t="n">
         <v>36.9</v>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>4</v>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -3063,7 +3578,9 @@
       <c r="I28" t="n">
         <v>31.3</v>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>8</v>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
@@ -3212,7 +3729,9 @@
       <c r="I31" t="n">
         <v>6.8</v>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>8</v>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
